--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>359200</v>
+      </c>
+      <c r="E8" s="3">
         <v>345400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>311000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>303000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>304000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>305100</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>269800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>241800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>273200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>361800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>327700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>320500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>358700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>824600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>965300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>838700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>786600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>745100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>524600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>395600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>375500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>320000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>274800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>192800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>353300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>423100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>112500</v>
+      </c>
+      <c r="E9" s="3">
         <v>125400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>123500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>124400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>114800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>98800</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>99900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>97900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>99000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>105500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>106700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>119800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>118200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>186500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>209400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>178000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>159900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>150600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>139900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>129600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>140000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>138500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>114100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>115300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>177200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>185500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>246800</v>
+      </c>
+      <c r="E10" s="3">
         <v>220000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>187500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>178600</v>
       </c>
-      <c r="G10" s="3">
-        <v>189100</v>
-      </c>
       <c r="H10" s="3">
+        <v>189200</v>
+      </c>
+      <c r="I10" s="3">
         <v>206300</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>169900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>143900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>174100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>256300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>221000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>200700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>240600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>638100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>755900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>660700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>626700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>594500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>384700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>266000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>235500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>181500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>160700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>77500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>176100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>237600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,19 +1259,22 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>417300</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1274,21 +1294,21 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>99300</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-9500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-152000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1296,126 +1316,132 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-192100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-23900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-22200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-610800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-662900</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>47800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>69700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1564900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>46100</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E15" s="3">
         <v>117600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>152700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>124900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>121500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>103200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>38300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>113100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>96300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>109400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>965500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>111700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>116600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>109500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>171900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>130200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>140800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>134200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>148200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>167800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>149700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>106000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>148200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>167700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>106700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>157800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>139900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>182300</v>
+      </c>
+      <c r="E17" s="3">
         <v>488500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>258900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>232600</v>
       </c>
-      <c r="G17" s="3">
-        <v>185300</v>
-      </c>
       <c r="H17" s="3">
+        <v>185000</v>
+      </c>
+      <c r="I17" s="3">
         <v>239600</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>205800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>286800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>213600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>940300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>247300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>209800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>195400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>417300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>388500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>373700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>167400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>319000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>332500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-279500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-366300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>338200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>375000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>341400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1956800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>422700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-143200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>52100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>70500</v>
       </c>
-      <c r="G18" s="3">
-        <v>118700</v>
-      </c>
       <c r="H18" s="3">
+        <v>119000</v>
+      </c>
+      <c r="I18" s="3">
         <v>65600</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>64000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-45000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>59500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-578500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>80500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>110600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>163300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>407300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>576800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>465000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>619200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>426100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>192100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>675100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>741800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-100200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-148600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,438 +1680,454 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E20" s="3">
         <v>11300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-30200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>30100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-2500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I20" s="3">
         <v>33600</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>9300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-31900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>477200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-141200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>53700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-324100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-376900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-139300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-51300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>47500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>57300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>37200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>284900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-36900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>234900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>165300</v>
       </c>
-      <c r="G21" s="3">
-        <v>242700</v>
-      </c>
       <c r="H21" s="3">
+        <v>243100</v>
+      </c>
+      <c r="I21" s="3">
         <v>135200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>38300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>167900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>54100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>154700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>389200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>177000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>259200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>260100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1056400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>565900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>659500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>429300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>561700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-17000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>685500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>796500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>115800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>45200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>177500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E22" s="3">
         <v>19100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>24700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22900</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>22500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>16300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>17900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>19200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>149700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-173600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-355200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15700</v>
       </c>
-      <c r="G23" s="3">
-        <v>93600</v>
-      </c>
       <c r="H23" s="3">
+        <v>93900</v>
+      </c>
+      <c r="I23" s="3">
         <v>9000</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>39100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-57600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-693000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>50400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>136800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>286400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>862000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>411200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>497600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>280200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>397200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-203500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>517000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>671300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-52200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-140000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-119000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>18400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-72400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-35700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>19100</v>
       </c>
-      <c r="G24" s="3">
-        <v>39000</v>
-      </c>
       <c r="H24" s="3">
+        <v>39100</v>
+      </c>
+      <c r="I24" s="3">
         <v>6400</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>38100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-84800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>40200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>466600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>140100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>135000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>52600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-56400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>65700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>171300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-70000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-47700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-247700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>17000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-101200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-319500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3400</v>
       </c>
-      <c r="G26" s="3">
-        <v>54500</v>
-      </c>
       <c r="H26" s="3">
+        <v>54800</v>
+      </c>
+      <c r="I26" s="3">
         <v>2700</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-79500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-608100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>42400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>96600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>281100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>395400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>271100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>362600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>284000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>344600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-147100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>451300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>500000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-57700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-69900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-71300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-104300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-319200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-171200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10400</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>38300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-60200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-608100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>96600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>281100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>395400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>271100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>362600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>284000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>344600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-147100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>451300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>500000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-57700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-69900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-71300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,41 +2479,44 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E29" s="3">
         <v>-3100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>5300</v>
       </c>
-      <c r="G29" s="3">
-        <v>-225700</v>
-      </c>
       <c r="H29" s="3">
+        <v>-226000</v>
+      </c>
+      <c r="I29" s="3">
         <v>7700</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>8800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>19300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>8100</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>30200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-30100</v>
       </c>
-      <c r="G32" s="3">
-        <v>2500</v>
-      </c>
       <c r="H32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-33600</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-9300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>31900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-477200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>141200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-53700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>324100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>376900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>139300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>51300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>22300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-47500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-57300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-37200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-104300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-319200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-171200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10400</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>38300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-60200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-608100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>42400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>96600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>281100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>395400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>271100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>362600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>284000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>344600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-147100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>451300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>500000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-57700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-69900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-71300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-104300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-319200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-171200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10400</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>38300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-60200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-608100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>42400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>96600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>281100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>395400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>271100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>362600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>284000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>344600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-147100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>451300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>500000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-57700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-69900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-71300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E41" s="3">
         <v>11700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>50700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>91600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>141300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>195600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>188100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>107100</v>
       </c>
-      <c r="N41" s="3" t="s">
+      <c r="O41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>38300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>73800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6000</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
         <v>0</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>3600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>29000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3308,8 +3398,8 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
@@ -3326,8 +3416,8 @@
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3350,405 +3440,420 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E43" s="3">
         <v>199900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>199500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>141100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>219700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>223400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>207500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>203100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>188900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>269700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>183900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>223000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>217400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>247300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>373700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>391200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>369400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>396700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>328600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>281600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>205900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>240500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>196100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>179400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>233000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>188400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>211400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E44" s="3">
         <v>28000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>34000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>46100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>33800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>28300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>21600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>33200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>43400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>19900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>16100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>19700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>30800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>25800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>23900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>20100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>22800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>28500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>24600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>17100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>21500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>15800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>29400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E45" s="3">
         <v>66100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>57400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>494900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>28000</v>
       </c>
       <c r="I45" s="3">
         <v>28000</v>
       </c>
       <c r="J45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K45" s="3">
         <v>68500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>71000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>118300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>237600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>195900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>246300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>249300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>307300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>168700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>134200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>126800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>118200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>155800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>58300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>31300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>44600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>65800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>83100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>123900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>77900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>402900</v>
+      </c>
+      <c r="E46" s="3">
         <v>347300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>340800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>283300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>859200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>354600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>404700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>482000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>541300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>654600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>623600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>485900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>561500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>631200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>714400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>598500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>530100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>551900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>472800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>460100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>292800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>261000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>267600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>342400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>344700</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>347700</v>
       </c>
       <c r="AD46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E47" s="3">
         <v>32600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>32000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>54900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>56600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>58700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>58500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>59300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>55500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>38500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>56400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>47800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>38100</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
@@ -3765,8 +3870,8 @@
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3780,94 +3885,100 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3386400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3497700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3492600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3882100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3929700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4470600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3643700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3848300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3790900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3796200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3847300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4644500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4708800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4602200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5962100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5646000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5421300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5175200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5057500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4915500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4816300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4071700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3361200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3352000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3553000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3531500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5301800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E52" s="3">
         <v>14300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>44300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>57600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>258100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>316300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>292100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>472000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>375000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>374000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>298400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>354800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>486900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>506800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>466700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>496200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>216700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3865400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3973600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3897700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4274200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4918500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4928400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4250400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4503600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4517500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4670600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4721900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5293800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5422100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5384400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6991100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6608600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6281600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6199100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5905300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5749600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5407500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4726500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4109100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4126400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4362100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4372300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5866100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,130 +4576,134 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>284600</v>
+      </c>
+      <c r="E57" s="3">
         <v>305800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>336600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>289000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>286800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>369800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>287200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>237600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>243300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>284900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>272100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>272500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>323600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>347300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>481400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>444700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>422800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>398900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>440700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>364500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>346500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>312000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>297700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>246700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>309600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>441800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>312400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E58" s="3">
         <v>5900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -4618,352 +4752,367 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>113200</v>
+      </c>
+      <c r="E59" s="3">
         <v>236400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>61100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>55100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>146600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>120900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>165900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>131100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>232600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>266500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>239100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>269600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>334000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>417200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>410600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>542300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>535800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>655900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>306200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>531500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>181700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>73300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>135500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>84200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>58800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>64500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>103800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>403200</v>
+      </c>
+      <c r="E60" s="3">
         <v>548100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>404400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>351400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>442500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>499600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>461600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>386100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>496500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>566600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>527100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>542200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>657600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>764500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>892000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>987100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>958700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1054900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>746800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>896000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>528200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>385300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>433100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>330900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>368400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>506300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>416200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>954300</v>
+      </c>
+      <c r="E61" s="3">
         <v>933600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>942800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>944200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1469400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1343400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>707800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>758800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>736900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>710700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>717100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>741700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>721000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>724200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1132900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1463400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1579300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1436100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1711800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1827400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1841500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1984200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2010400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2153200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2220700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2085300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2017700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>774400</v>
+      </c>
+      <c r="E62" s="3">
         <v>813000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>698800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>751100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>748900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>816900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>873700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>946800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>940300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>916400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>893600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>838800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>797300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>743100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1565100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1268100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1062100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1379600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1380600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1290800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1176000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>946500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>740200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>663200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>742300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>628400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>978900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2342900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2508800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2277200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2329900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2943500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2923800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2296700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2372800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2449300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2468300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2426200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2446000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2535100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2590900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3590000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3718600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3600100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3870600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3839200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4014300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3545700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3315900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3183700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3147300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3331400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3220000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3412800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1427900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1534700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1444300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1098700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1115700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-889200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-895800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-937800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-973600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-926500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-956800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-338600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-380200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-463200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1522500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1464800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1620500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1944300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1975000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2004600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1953600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2130800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2068200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2202300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2295600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2847800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2887100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2793500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3401100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2889900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2681500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2328500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2066100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1735400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1861800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1410600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>925400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>979100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1030700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1152300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2453300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-104300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-319200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-171200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10400</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>38300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-60200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-608100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>42400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>96600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>281100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>395400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>271100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>362600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>284000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>344600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-147100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>451300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>500000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-57700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-69900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-71300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,94 +6605,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>121500</v>
+      </c>
+      <c r="E83" s="3">
         <v>122700</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>133400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>117800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>131800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>196100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>111700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>116600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>109500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>127000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>94800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>109300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>107500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>171900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>130200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>140800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>134200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>148200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>167800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>149700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>106000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>148200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>167700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>106700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>157800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>139900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E89" s="3">
         <v>162900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>97300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>279600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>103000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>195100</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>99600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>194600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>261600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>260400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>87600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>131100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>287200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>495200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>447600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>530400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>341100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>250400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>211500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>253400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>119100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>135100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>93800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>278400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>220500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,94 +7261,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-96400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-139900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-104500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-84700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-126700</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-89800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-84800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-140900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-110200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-95200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-127700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-213600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-172900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-186200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-611000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-92100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-172700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-158600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-79900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-135200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-79500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>233400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-145900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-873700</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-107900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-111800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-133900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-126000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-124200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-80300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-168100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-168300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-612600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-110300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-134900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-162900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-97200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-74700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-50600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-41800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-122000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-187000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-117000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,59 +7650,60 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E96" s="3">
         <v>14800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>29100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>14400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>14700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>12900</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>14100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>14000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>12000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>12400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>12100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>12300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>9700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-13000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-10000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -7492,19 +7726,22 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-17400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-100300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-97300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-29700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-37100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-530100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>76400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>602500</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-48700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-72700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-44800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-61800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-34100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-143500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-323000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-272500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>78500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-231400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-108000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-48400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-159900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-47200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-83200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-51200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>118200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-104400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-85200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>33500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-75300</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-56800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>83600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>107100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-37500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-37100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>63600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6000</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-3600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-24800</v>
       </c>
     </row>
